--- a/data/gravel/Lauf Siegla 2025.xlsx
+++ b/data/gravel/Lauf Siegla 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6171503-5A9E-6944-BBF7-742D81070197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E486E36-4EBC-7B48-8769-986132A171EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3580" yWindow="2940" windowWidth="25220" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="138">
   <si>
     <t>brand</t>
   </si>
@@ -1960,8 +1960,8 @@
       <c r="A45" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>133</v>
+      <c r="B45" s="6">
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:7">

--- a/data/gravel/Lauf Siegla 2025.xlsx
+++ b/data/gravel/Lauf Siegla 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E486E36-4EBC-7B48-8769-986132A171EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137A2A7E-4D47-2E47-B8C8-602E7FDF6572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3580" yWindow="2940" windowWidth="25220" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="139">
   <si>
     <t>brand</t>
   </si>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t>* measuremens based on 6 mm sag (this is 20% of 30 mm)</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -2139,6 +2142,9 @@
       <c r="A73" t="s">
         <v>93</v>
       </c>
+      <c r="B73" s="6" t="s">
+        <v>138</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/gravel/Lauf Siegla 2025.xlsx
+++ b/data/gravel/Lauf Siegla 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137A2A7E-4D47-2E47-B8C8-602E7FDF6572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59151796-2FFB-B64D-ABB8-93D21536280D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3580" yWindow="2940" windowWidth="25220" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="141">
   <si>
     <t>brand</t>
   </si>
@@ -450,6 +450,12 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://www.laufcycles.com/product/lauf-seigla?utm_term=lauf%20seigla&amp;utm_campaign=%5BSearch%5D+Gravel+bikes+-+US&amp;utm_source=adwords&amp;utm_medium=ppc&amp;hsa_acc=7080349541&amp;hsa_cam=22336476166&amp;hsa_grp=180030440767&amp;hsa_ad=738489692108&amp;hsa_src=g&amp;hsa_tgt=kwd-1961602049897&amp;hsa_kw=lauf%20seigla&amp;hsa_mt=p&amp;hsa_net=adwords&amp;hsa_ver=3&amp;gad_source=1&amp;gad_campaignid=22336476166&amp;gbraid=0AAAAACTmLZZw8tSLVe1JxUoXaLDYK-IKx&amp;gclid=Cj0KCQjw6bfHBhDNARIsAIGsqLiUGntIF6v4XRW2viiqFTZeQxD8hOrGoym-LVB_9niElhw9UAe8UaEaAuxPEALw_wcB</t>
+  </si>
+  <si>
+    <t>https://www.laufcycles.com/_next/image?url=https%3A%2F%2Fimages.prismic.io%2Flauf%2FaFAN1bNJEFaPX_Xs_Lauf-Sram_WEBSITE-12.jpg%3Fauto%3Dformat%2Ccompress%26rect%3D0%2C0%2C4000%2C2250%26w%3D1280%26h%3D720&amp;w=1920&amp;q=75</t>
   </si>
 </sst>
 </file>
@@ -859,6 +865,14 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
+      <c r="B5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">

--- a/data/gravel/Lauf Siegla 2025.xlsx
+++ b/data/gravel/Lauf Siegla 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59151796-2FFB-B64D-ABB8-93D21536280D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C485A39A-E147-F74E-A4D4-50FFCB222A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3580" yWindow="2940" windowWidth="25220" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="143">
   <si>
     <t>brand</t>
   </si>
@@ -456,6 +456,12 @@
   </si>
   <si>
     <t>https://www.laufcycles.com/_next/image?url=https%3A%2F%2Fimages.prismic.io%2Flauf%2FaFAN1bNJEFaPX_Xs_Lauf-Sram_WEBSITE-12.jpg%3Fauto%3Dformat%2Ccompress%26rect%3D0%2C0%2C4000%2C2250%26w%3D1280%26h%3D720&amp;w=1920&amp;q=75</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Reykjavík, Iceland</t>
   </si>
 </sst>
 </file>
@@ -823,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2160,6 +2166,14 @@
         <v>138</v>
       </c>
     </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I9:I10"/>

--- a/data/gravel/Lauf Siegla 2025.xlsx
+++ b/data/gravel/Lauf Siegla 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C485A39A-E147-F74E-A4D4-50FFCB222A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E75C19A-60F2-294C-9825-D6124717340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3580" yWindow="2940" windowWidth="25220" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="149">
   <si>
     <t>brand</t>
   </si>
@@ -462,6 +462,24 @@
   </si>
   <si>
     <t>Reykjavík, Iceland</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -829,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2015,162 +2033,192 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>70</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>72</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>76</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>70</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>77</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>80</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="B62">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>84</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>85</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B70">
-        <v>2290</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B71">
-        <v>3350</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>93</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>90</v>
+      </c>
+      <c r="B76">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B77">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>93</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>141</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>142</v>
       </c>
     </row>
